--- a/SGC-CKN/Excel/c6c61a37-5fe1-4346-a0a4-cd723bf56b71_Lô_CT-02_P7-17_D800_05-04-2026.xlsx
+++ b/SGC-CKN/Excel/c6c61a37-5fe1-4346-a0a4-cd723bf56b71_Lô_CT-02_P7-17_D800_05-04-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="77">
   <si>
     <t>Dự án</t>
   </si>
@@ -98,11 +98,11 @@
     <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
   </si>
   <si>
-    <t xml:space="preserve">19:00
+    <t xml:space="preserve">18:00
 04/04/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">19:20
+    <t xml:space="preserve">18:20
 04/04/2026</t>
   </si>
   <si>
@@ -115,20 +115,24 @@
     <t>Cát pha xám ghi, xám nâu TT dẻo</t>
   </si>
   <si>
-    <t xml:space="preserve">19:21
+    <t xml:space="preserve">18:21
 04/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18:40
+04/04/2026</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Sét xám trắng, xám xanh dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">19:40
 04/04/2026</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>Sét xám trắng, xám xanh dẻo chảy</t>
-  </si>
-  <si>
     <t xml:space="preserve">20:20
 04/04/2026</t>
   </si>
@@ -210,11 +214,11 @@
   </si>
   <si>
     <t xml:space="preserve">01:00
-04/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02:14
-04/04/2026</t>
+05/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02:44
+05/04/2026</t>
   </si>
   <si>
     <t>10</t>
@@ -224,11 +228,11 @@
   </si>
   <si>
     <t xml:space="preserve">02:45
-04/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09:35
-04/04/2026</t>
+05/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03:35
+05/04/2026</t>
   </si>
   <si>
     <t>ẢNH BIÊN BẢN GỐC</t>
@@ -265,7 +269,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -348,12 +352,6 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
       <sz val="12"/>
       <name val="Arial"/>
     </font>
@@ -364,7 +362,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -418,17 +416,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFD9F99D"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFED7AA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -444,11 +442,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF99F6E4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC2626"/>
       </patternFill>
     </fill>
     <fill>
@@ -544,7 +537,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -606,26 +599,26 @@
     <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -654,16 +647,13 @@
     <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1249,7 +1239,7 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-0.553</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
         <v>-6.92</v>
@@ -1258,10 +1248,10 @@
         <v>0.33</v>
       </c>
       <c r="I11" s="5">
-        <v>6.37</v>
+        <v>6.92</v>
       </c>
       <c r="J11" s="8">
-        <v>19.1</v>
+        <v>20.76</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1313,10 +1303,10 @@
         <v>36</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F13" s="12">
         <v>-9.86</v>
@@ -1339,34 +1329,34 @@
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B14" s="15" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F14" s="15">
         <v>-17.45</v>
       </c>
       <c r="G14" s="15">
-        <v>-24.26</v>
+        <v>-21.26</v>
       </c>
       <c r="H14" s="15">
         <v>0.4</v>
       </c>
       <c r="I14" s="15">
-        <v>6.81</v>
+        <v>3.81</v>
       </c>
       <c r="J14" s="8">
-        <v>17.03</v>
+        <v>9.53</v>
       </c>
       <c r="K14" s="16" t="s">
         <v>30</v>
@@ -1374,124 +1364,124 @@
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B15" s="18" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F15" s="18">
-        <v>-24.26</v>
+        <v>-21.26</v>
       </c>
       <c r="G15" s="18">
-        <v>-26.54</v>
+        <v>-26.52</v>
       </c>
       <c r="H15" s="18">
         <v>0.57</v>
       </c>
       <c r="I15" s="18">
-        <v>2.28</v>
-      </c>
-      <c r="J15" s="21">
-        <v>4.02</v>
+        <v>5.26</v>
+      </c>
+      <c r="J15" s="8">
+        <v>9.28</v>
       </c>
       <c r="K15" s="19" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="B16" s="22" t="s">
+      <c r="A16" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="D16" s="24" t="s">
+      <c r="C16" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="E16" s="24" t="s">
+      <c r="D16" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="F16" s="22">
-        <v>-26.54</v>
-      </c>
-      <c r="G16" s="22">
-        <v>-36.14</v>
-      </c>
-      <c r="H16" s="22">
+      <c r="E16" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="F16" s="21">
+        <v>-26.52</v>
+      </c>
+      <c r="G16" s="21">
+        <v>-36.11</v>
+      </c>
+      <c r="H16" s="21">
         <v>0.98</v>
       </c>
-      <c r="I16" s="22">
-        <v>9.6</v>
+      <c r="I16" s="21">
+        <v>9.59</v>
       </c>
       <c r="J16" s="8">
-        <v>9.76</v>
-      </c>
-      <c r="K16" s="23" t="s">
+        <v>9.75</v>
+      </c>
+      <c r="K16" s="22" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="B17" s="25" t="s">
+      <c r="A17" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="B17" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="D17" s="27" t="s">
+      <c r="C17" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="E17" s="27" t="s">
+      <c r="D17" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="F17" s="25">
-        <v>-36.14</v>
-      </c>
-      <c r="G17" s="25">
+      <c r="E17" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="F17" s="24">
+        <v>-36.11</v>
+      </c>
+      <c r="G17" s="24">
         <v>-37.2</v>
       </c>
-      <c r="H17" s="25">
+      <c r="H17" s="24">
         <v>0.4</v>
       </c>
-      <c r="I17" s="25">
-        <v>1.06</v>
-      </c>
-      <c r="J17" s="21">
-        <v>2.65</v>
-      </c>
-      <c r="K17" s="26" t="s">
+      <c r="I17" s="24">
+        <v>1.09</v>
+      </c>
+      <c r="J17" s="27">
+        <v>2.73</v>
+      </c>
+      <c r="K17" s="25" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B18" s="28" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D18" s="30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E18" s="30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F18" s="28">
         <v>-37.2</v>
@@ -1505,7 +1495,7 @@
       <c r="I18" s="28">
         <v>2.3</v>
       </c>
-      <c r="J18" s="21">
+      <c r="J18" s="27">
         <v>4.45</v>
       </c>
       <c r="K18" s="29" t="s">
@@ -1514,34 +1504,34 @@
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="31" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B19" s="31" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="32" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D19" s="33" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F19" s="31">
         <v>-39.5</v>
       </c>
       <c r="G19" s="31">
-        <v>-43.08</v>
+        <v>-43.88</v>
       </c>
       <c r="H19" s="31">
-        <v>1.23</v>
+        <v>1.73</v>
       </c>
       <c r="I19" s="31">
-        <v>3.58</v>
-      </c>
-      <c r="J19" s="21">
-        <v>2.9</v>
+        <v>4.38</v>
+      </c>
+      <c r="J19" s="27">
+        <v>2.53</v>
       </c>
       <c r="K19" s="32" t="s">
         <v>30</v>
@@ -1549,53 +1539,53 @@
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="34" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B20" s="34" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="35" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D20" s="36" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E20" s="36" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F20" s="34">
-        <v>-43.08</v>
+        <v>-43.88</v>
       </c>
       <c r="G20" s="34">
         <v>-44.9</v>
       </c>
       <c r="H20" s="34">
-        <v>6.83</v>
+        <v>0.83</v>
       </c>
       <c r="I20" s="34">
-        <v>1.82</v>
-      </c>
-      <c r="J20" s="37">
-        <v>0.27</v>
+        <v>1.02</v>
+      </c>
+      <c r="J20" s="27">
+        <v>1.22</v>
       </c>
       <c r="K20" s="35" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="38" t="s">
-        <v>66</v>
-      </c>
-      <c r="B23" s="38"/>
-      <c r="C23" s="38"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="38"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="38"/>
-      <c r="J23" s="38"/>
-      <c r="K23" s="38"/>
+      <c r="A23" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="B23" s="37"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="37"/>
+      <c r="G23" s="37"/>
+      <c r="H23" s="37"/>
+      <c r="I23" s="37"/>
+      <c r="J23" s="37"/>
+      <c r="K23" s="37"/>
     </row>
     <row r="24" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1690,31 +1680,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1731,7 +1721,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-0.55</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
         <v>-6.92</v>
@@ -1740,10 +1730,10 @@
         <v>0.33</v>
       </c>
       <c r="H2" s="5">
-        <v>6.37</v>
+        <v>6.92</v>
       </c>
       <c r="I2" s="8">
-        <v>19.1</v>
+        <v>20.76</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1812,7 +1802,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D5" s="15">
         <v>1</v>
@@ -1821,16 +1811,16 @@
         <v>-17.45</v>
       </c>
       <c r="F5" s="15">
-        <v>-24.26</v>
+        <v>-21.26</v>
       </c>
       <c r="G5" s="15">
         <v>0.4</v>
       </c>
       <c r="H5" s="15">
-        <v>6.81</v>
+        <v>3.81</v>
       </c>
       <c r="I5" s="8">
-        <v>17.03</v>
+        <v>9.53</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1841,83 +1831,83 @@
         <v>11</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D6" s="18">
         <v>1</v>
       </c>
       <c r="E6" s="18">
-        <v>-24.26</v>
+        <v>-21.26</v>
       </c>
       <c r="F6" s="18">
-        <v>-26.54</v>
+        <v>-26.52</v>
       </c>
       <c r="G6" s="18">
         <v>0.57</v>
       </c>
       <c r="H6" s="18">
-        <v>2.28</v>
-      </c>
-      <c r="I6" s="21">
-        <v>4.02</v>
+        <v>5.26</v>
+      </c>
+      <c r="I6" s="8">
+        <v>9.28</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="22">
+      <c r="A7" s="21">
         <v>6</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="D7" s="22">
+      <c r="C7" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="21">
         <v>1</v>
       </c>
-      <c r="E7" s="22">
-        <v>-26.54</v>
-      </c>
-      <c r="F7" s="22">
-        <v>-36.14</v>
-      </c>
-      <c r="G7" s="22">
+      <c r="E7" s="21">
+        <v>-26.52</v>
+      </c>
+      <c r="F7" s="21">
+        <v>-36.11</v>
+      </c>
+      <c r="G7" s="21">
         <v>0.98</v>
       </c>
-      <c r="H7" s="22">
-        <v>9.6</v>
+      <c r="H7" s="21">
+        <v>9.59</v>
       </c>
       <c r="I7" s="8">
-        <v>9.76</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="25">
+      <c r="A8" s="24">
         <v>7</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="D8" s="25">
+      <c r="C8" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="24">
         <v>1</v>
       </c>
-      <c r="E8" s="25">
-        <v>-36.14</v>
-      </c>
-      <c r="F8" s="25">
+      <c r="E8" s="24">
+        <v>-36.11</v>
+      </c>
+      <c r="F8" s="24">
         <v>-37.2</v>
       </c>
-      <c r="G8" s="25">
+      <c r="G8" s="24">
         <v>0.4</v>
       </c>
-      <c r="H8" s="25">
-        <v>1.06</v>
-      </c>
-      <c r="I8" s="21">
-        <v>2.65</v>
+      <c r="H8" s="24">
+        <v>1.09</v>
+      </c>
+      <c r="I8" s="27">
+        <v>2.73</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1928,7 +1918,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
@@ -1945,7 +1935,7 @@
       <c r="H9" s="28">
         <v>2.3</v>
       </c>
-      <c r="I9" s="21">
+      <c r="I9" s="27">
         <v>4.45</v>
       </c>
     </row>
@@ -1957,7 +1947,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D10" s="31">
         <v>1</v>
@@ -1966,16 +1956,16 @@
         <v>-39.5</v>
       </c>
       <c r="F10" s="31">
-        <v>-43.08</v>
+        <v>-43.88</v>
       </c>
       <c r="G10" s="31">
-        <v>1.23</v>
+        <v>1.73</v>
       </c>
       <c r="H10" s="31">
-        <v>3.58</v>
-      </c>
-      <c r="I10" s="21">
-        <v>2.9</v>
+        <v>4.38</v>
+      </c>
+      <c r="I10" s="27">
+        <v>2.53</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1986,54 +1976,54 @@
         <v>11</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D11" s="34">
         <v>1</v>
       </c>
       <c r="E11" s="34">
-        <v>-43.08</v>
+        <v>-43.88</v>
       </c>
       <c r="F11" s="34">
         <v>-44.9</v>
       </c>
       <c r="G11" s="34">
-        <v>6.83</v>
+        <v>0.83</v>
       </c>
       <c r="H11" s="34">
-        <v>1.82</v>
-      </c>
-      <c r="I11" s="37">
-        <v>0.27</v>
+        <v>1.02</v>
+      </c>
+      <c r="I11" s="27">
+        <v>1.22</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="39" t="s">
-        <v>75</v>
-      </c>
-      <c r="B12" s="40" t="s">
+      <c r="A12" s="38" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="40" t="s">
+      <c r="C12" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="40">
+      <c r="D12" s="39">
         <v>10</v>
       </c>
-      <c r="E12" s="40">
-        <v>-0.55</v>
-      </c>
-      <c r="F12" s="40">
+      <c r="E12" s="39">
+        <v>0</v>
+      </c>
+      <c r="F12" s="39">
         <v>-44.9</v>
       </c>
-      <c r="G12" s="40">
-        <v>12.25</v>
-      </c>
-      <c r="H12" s="40">
-        <v>44.35</v>
-      </c>
-      <c r="I12" s="40">
-        <v>3.62</v>
+      <c r="G12" s="39">
+        <v>6.75</v>
+      </c>
+      <c r="H12" s="39">
+        <v>44.9</v>
+      </c>
+      <c r="I12" s="39">
+        <v>6.65</v>
       </c>
     </row>
   </sheetData>
